--- a/Fall 2025/Controls Lab/Lab 2/outputs/tables/metrics_all_runs.xlsx
+++ b/Fall 2025/Controls Lab/Lab 2/outputs/tables/metrics_all_runs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noaht\School\Fall 2025\Controls Lab\Lab 2\outputs\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ABDBE6-14E3-4F5E-9801-C3919F3C8D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B03074-819F-4602-9F0C-813BCC15CFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="10590" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="54">
   <si>
     <t>file</t>
   </si>
@@ -131,13 +131,64 @@
   </si>
   <si>
     <t>PID_prop</t>
+  </si>
+  <si>
+    <t>Waveform</t>
+  </si>
+  <si>
+    <t>Deadband (°)</t>
+  </si>
+  <si>
+    <t>Duty Cycle</t>
+  </si>
+  <si>
+    <t>Mean(cmd)</t>
+  </si>
+  <si>
+    <t>Std(cmd)</t>
+  </si>
+  <si>
+    <t>RMS(cmd)</t>
+  </si>
+  <si>
+    <t>Mean(err °)</t>
+  </si>
+  <si>
+    <t>Std(err °)</t>
+  </si>
+  <si>
+    <t>RMS(err °)</t>
+  </si>
+  <si>
+    <t>Sine</t>
+  </si>
+  <si>
+    <t>–0.09</t>
+  </si>
+  <si>
+    <t>Square</t>
+  </si>
+  <si>
+    <t>–0.38</t>
+  </si>
+  <si>
+    <t>Sinusoidal</t>
+  </si>
+  <si>
+    <t>−0.03</t>
+  </si>
+  <si>
+    <t>−30.02</t>
+  </si>
+  <si>
+    <t>−0.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +200,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -186,10 +245,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -493,9 +561,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="21.5703125" customWidth="1"/>
     <col min="12" max="12" width="19.5703125" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
@@ -503,6 +572,9 @@
     <col min="16" max="16" width="14.85546875" customWidth="1"/>
     <col min="17" max="17" width="15.85546875" customWidth="1"/>
     <col min="18" max="18" width="16.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" customWidth="1"/>
+    <col min="21" max="21" width="21.42578125" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1497,7 +1569,7 @@
         <v>26</v>
       </c>
       <c r="L16">
-        <v>0.2485800510281771</v>
+        <v>0.24858005102817701</v>
       </c>
       <c r="M16">
         <v>45.338003557290463</v>
@@ -1648,7 +1720,7 @@
         <v>7880</v>
       </c>
       <c r="U18">
-        <v>65.151515151514985</v>
+        <v>65.151515151515</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -1950,6 +2022,375 @@
       </c>
       <c r="S23">
         <v>3928</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="3">
+        <v>62.91</v>
+      </c>
+      <c r="F30" s="3">
+        <v>30.49</v>
+      </c>
+      <c r="G30" s="3">
+        <v>69.91</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I30" s="3">
+        <v>6.44</v>
+      </c>
+      <c r="J30" s="3">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3">
+        <v>5</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="3">
+        <v>63.02</v>
+      </c>
+      <c r="F31" s="3">
+        <v>30.45</v>
+      </c>
+      <c r="G31" s="3">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="J31" s="3">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3">
+        <v>10</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>63.01</v>
+      </c>
+      <c r="F32" s="3">
+        <v>30.42</v>
+      </c>
+      <c r="G32" s="3">
+        <v>69.97</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1.51</v>
+      </c>
+      <c r="I32" s="3">
+        <v>7.72</v>
+      </c>
+      <c r="J32" s="3">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="3">
+        <v>99.01</v>
+      </c>
+      <c r="G33" s="3">
+        <v>99</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I33" s="3">
+        <v>61.98</v>
+      </c>
+      <c r="J33" s="3">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="F34" s="3">
+        <v>99.01</v>
+      </c>
+      <c r="G34" s="3">
+        <v>99</v>
+      </c>
+      <c r="H34" s="3">
+        <v>6.64</v>
+      </c>
+      <c r="I34" s="3">
+        <v>57.51</v>
+      </c>
+      <c r="J34" s="3">
+        <v>57.89</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3">
+        <v>10</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" s="3">
+        <v>99.01</v>
+      </c>
+      <c r="G35" s="3">
+        <v>99</v>
+      </c>
+      <c r="H35" s="3">
+        <v>6.71</v>
+      </c>
+      <c r="I35" s="3">
+        <v>43.67</v>
+      </c>
+      <c r="J35" s="3">
+        <v>44.18</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="D39" s="3">
+        <v>63.26</v>
+      </c>
+      <c r="E39" s="3">
+        <v>30.22</v>
+      </c>
+      <c r="F39" s="3">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="G39" s="3">
+        <v>24.73</v>
+      </c>
+      <c r="H39" s="3">
+        <v>30.2</v>
+      </c>
+      <c r="I39" s="3">
+        <v>39.049999999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3">
+        <v>2</v>
+      </c>
+      <c r="D40" s="3">
+        <v>63.09</v>
+      </c>
+      <c r="E40" s="3">
+        <v>30.47</v>
+      </c>
+      <c r="F40" s="3">
+        <v>70.06</v>
+      </c>
+      <c r="G40" s="3">
+        <v>48.71</v>
+      </c>
+      <c r="H40" s="3">
+        <v>36.1</v>
+      </c>
+      <c r="I40" s="3">
+        <v>60.63</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3">
+        <v>5</v>
+      </c>
+      <c r="D41" s="3">
+        <v>62.99</v>
+      </c>
+      <c r="E41" s="3">
+        <v>30.56</v>
+      </c>
+      <c r="F41" s="3">
+        <v>70.010000000000005</v>
+      </c>
+      <c r="G41" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="H41" s="3">
+        <v>28.5</v>
+      </c>
+      <c r="I41" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="3">
+        <v>99.01</v>
+      </c>
+      <c r="F42" s="3">
+        <v>99</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42" s="3">
+        <v>99</v>
+      </c>
+      <c r="I42" s="3">
+        <v>103.4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E43" s="3">
+        <v>99.01</v>
+      </c>
+      <c r="F43" s="3">
+        <v>99</v>
+      </c>
+      <c r="G43" s="3">
+        <v>2.94</v>
+      </c>
+      <c r="H43" s="3">
+        <v>71.3</v>
+      </c>
+      <c r="I43" s="3">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3">
+        <v>5</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="3">
+        <v>99.01</v>
+      </c>
+      <c r="F44" s="3">
+        <v>99</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3.28</v>
+      </c>
+      <c r="H44" s="3">
+        <v>47</v>
+      </c>
+      <c r="I44" s="3">
+        <v>47.1</v>
       </c>
     </row>
   </sheetData>
